--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\template_state_3.3\trans\VSbS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\trans\VSbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB33E179-2A35-4107-A4E5-723DF914CE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CD04216-85BC-4523-9C8B-BD5B0166732F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="13035" windowHeight="16890" firstSheet="2" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,19 +33,32 @@
     <definedName name="YEAR">#REF!</definedName>
     <definedName name="YEAR2">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="108">
   <si>
     <t>VSbS Vehicle Shares by Subregion</t>
   </si>
   <si>
-    <t>Louisiana</t>
-  </si>
-  <si>
     <t>Source:</t>
   </si>
   <si>
@@ -59,249 +72,6 @@
   </si>
   <si>
     <t>Table MV-1 (State motor-vehicle registrations)</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>This variable is used for a share of sales by subregion, but you can use share of total number of registered</t>
-  </si>
-  <si>
-    <t>vehicles in each subregion as a proxy for share of sales.</t>
-  </si>
-  <si>
-    <t>U.S. Data Notes</t>
-  </si>
-  <si>
-    <t>The categories the Federal Highway Administration uses are: automobiles, buses, trucks, and motorcycles.</t>
-  </si>
-  <si>
-    <t>We use the "automobile" shares to represent all passenger LDVs in the EPS, even though passenger LDVs</t>
-  </si>
-  <si>
-    <t>include passenger SUVs, which are technically light trucks.  The state-by-state distribution of</t>
-  </si>
-  <si>
-    <t>SUVs ought to be similar to the state-by-state distribution of automobiles.</t>
-  </si>
-  <si>
-    <t>We use the "truck" shares to represent both freight LDVs and freight HDVs in the EPS.</t>
-  </si>
-  <si>
-    <t>Adapting this Variable to Other EPS Regions</t>
-  </si>
-  <si>
-    <t>If you are adapting the EPS to another country or region and don't want to use</t>
-  </si>
-  <si>
-    <t>sub-regional ZEV mandates, simply put "1" in the first sub-region row for each type of road</t>
-  </si>
-  <si>
-    <t>vehicle and put "0" in all other cells on the blue output tabs.</t>
-  </si>
-  <si>
-    <t>STATE MOTOR-VEHICLE REGISTRATIONS - 2020</t>
-  </si>
-  <si>
-    <t>June 2022</t>
-  </si>
-  <si>
-    <t>TABLE MV-1</t>
-  </si>
-  <si>
-    <t>AUTOMOBILES</t>
-  </si>
-  <si>
-    <t>BUSES</t>
-  </si>
-  <si>
-    <t>TRUCKS</t>
-  </si>
-  <si>
-    <t>MOTORCYCLES</t>
-  </si>
-  <si>
-    <t>ALL MOTOR VEHICLES</t>
-  </si>
-  <si>
-    <t>STATE</t>
-  </si>
-  <si>
-    <t>PRIVATE AND</t>
-  </si>
-  <si>
-    <t>COMMERCIAL</t>
-  </si>
-  <si>
-    <t>PUBLICLY</t>
-  </si>
-  <si>
-    <t>(INCLUDING</t>
-  </si>
-  <si>
-    <t>OWNED</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWNED </t>
-  </si>
-  <si>
-    <t>TAXICABS)</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alaska </t>
-  </si>
-  <si>
-    <t>Arizona</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colorado </t>
-  </si>
-  <si>
-    <t>Connecticut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delaware </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dist. of Col. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgia </t>
-  </si>
-  <si>
-    <t>Hawaii</t>
-  </si>
-  <si>
-    <t>Idaho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Illinois </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indiana </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iowa </t>
-  </si>
-  <si>
-    <t>Kansas</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maine </t>
-  </si>
-  <si>
-    <t>Maryland</t>
-  </si>
-  <si>
-    <t>Massachusetts (2)</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minnesota </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mississippi </t>
-  </si>
-  <si>
-    <t>Missouri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montana </t>
-  </si>
-  <si>
-    <t>Nebraska</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nevada </t>
-  </si>
-  <si>
-    <t>New Hampshire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Jersey </t>
-  </si>
-  <si>
-    <t>New Mexico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York </t>
-  </si>
-  <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
-    <t>North Dakota</t>
-  </si>
-  <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oklahoma  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon </t>
-  </si>
-  <si>
-    <t>Pennsylvania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhode Island </t>
-  </si>
-  <si>
-    <t>South Carolina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tennessee </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texas </t>
-  </si>
-  <si>
-    <t>Utah</t>
-  </si>
-  <si>
-    <t>Vermont</t>
-  </si>
-  <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washington </t>
-  </si>
-  <si>
-    <t>West Virginia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wisconsin </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wyoming </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Total</t>
   </si>
   <si>
     <t>Sums may not equal to totals due to rounding.
@@ -309,31 +79,259 @@
 (2) Some data estimated by FHWA using secondary data sources due to data quality concerns.</t>
   </si>
   <si>
+    <t xml:space="preserve">   Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wyoming </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wisconsin </t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington </t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tennessee </t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota </t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhode Island </t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oregon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oklahoma  </t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York </t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Jersey </t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nevada </t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montana </t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mississippi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minnesota </t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Massachusetts (2)</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maine </t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iowa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indiana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illinois </t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dist. of Col. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delaware </t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colorado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">California </t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alaska </t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TAXICABS)</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>OWNED</t>
+  </si>
+  <si>
+    <t>COMMERCIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWNED </t>
+  </si>
+  <si>
+    <t>(INCLUDING</t>
+  </si>
+  <si>
+    <t>PUBLICLY</t>
+  </si>
+  <si>
+    <t>PRIVATE AND</t>
+  </si>
+  <si>
+    <t>STATE</t>
+  </si>
+  <si>
+    <t>ALL MOTOR VEHICLES</t>
+  </si>
+  <si>
+    <t>MOTORCYCLES</t>
+  </si>
+  <si>
+    <t>TRUCKS</t>
+  </si>
+  <si>
+    <t>BUSES</t>
+  </si>
+  <si>
+    <t>AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>TABLE MV-1</t>
+  </si>
+  <si>
+    <t>June 2022</t>
+  </si>
+  <si>
+    <t>STATE MOTOR-VEHICLE REGISTRATIONS - 2020</t>
+  </si>
+  <si>
+    <t>LDVs</t>
+  </si>
+  <si>
+    <t>HDVs</t>
+  </si>
+  <si>
+    <t>aircraft</t>
+  </si>
+  <si>
+    <t>rail</t>
+  </si>
+  <si>
+    <t>ships</t>
+  </si>
+  <si>
+    <t>motorbikes</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>District of Columbia</t>
+  </si>
+  <si>
     <t>Unit: dimensionless (share of vehicles)</t>
   </si>
   <si>
-    <t>LDVs</t>
-  </si>
-  <si>
-    <t>HDVs</t>
-  </si>
-  <si>
-    <t>aircraft</t>
-  </si>
-  <si>
-    <t>rail</t>
-  </si>
-  <si>
-    <t>ships</t>
-  </si>
-  <si>
-    <t>motorbikes</t>
-  </si>
-  <si>
-    <t>District of Columbia</t>
-  </si>
-  <si>
-    <t>Massachusetts</t>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>The categories the Federal Highway Administration uses are: automobiles, buses, trucks, and motorcycles.</t>
+  </si>
+  <si>
+    <t>SUVs ought to be similar to the state-by-state distribution of automobiles.</t>
+  </si>
+  <si>
+    <t>We use the "truck" shares to represent both freight LDVs and freight HDVs in the EPS.</t>
+  </si>
+  <si>
+    <t>We use the "automobile" shares to represent all passenger LDVs in the EPS, even though passenger LDVs</t>
+  </si>
+  <si>
+    <t>include passenger SUVs, which are technically light trucks.  The state-by-state distribution of</t>
   </si>
   <si>
     <t>subregion52</t>
@@ -361,6 +359,27 @@
   </si>
   <si>
     <t>subregion60</t>
+  </si>
+  <si>
+    <t>Adapting this Variable to Other EPS Regions</t>
+  </si>
+  <si>
+    <t>If you are adapting the EPS to another country or region and don't want to use</t>
+  </si>
+  <si>
+    <t>vehicle and put "0" in all other cells on the blue output tabs.</t>
+  </si>
+  <si>
+    <t>sub-regional ZEV mandates, simply put "1" in the first sub-region row for each type of road</t>
+  </si>
+  <si>
+    <t>This variable is used for a share of sales by subregion, but you can use share of total number of registered</t>
+  </si>
+  <si>
+    <t>vehicles in each subregion as a proxy for share of sales.</t>
+  </si>
+  <si>
+    <t>U.S. Data Notes</t>
   </si>
 </sst>
 </file>
@@ -371,7 +390,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0_);[Red]\(#,##0\);\—_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,6 +464,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -466,7 +491,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -1031,9 +1056,7 @@
       <left style="thin">
         <color indexed="8"/>
       </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="8"/>
       </top>
@@ -1042,27 +1065,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color indexed="8"/>
-      </left>
-      <right style="double">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="37" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="37" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="115">
@@ -1097,7 +1107,7 @@
     </xf>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="7" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1112,7 +1122,7 @@
     </xf>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="20" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="20" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="18" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1120,17 +1130,18 @@
     <xf numFmtId="38" fontId="5" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="5" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="26" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="27" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="27" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="28" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="29" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="29" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="5" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1144,9 +1155,11 @@
     <xf numFmtId="38" fontId="5" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1237,39 +1250,42 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="37" fontId="4" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="37" fontId="8" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="8" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="37" fontId="5" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="37" fontId="5" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="5" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="37" fontId="5" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="37" fontId="5" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Comma 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Comma 2" xfId="5" xr:uid="{7B2DBB66-964B-4992-8A85-CF7563C0181E}"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 3 2 4 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 5" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 8 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{E09E58F7-B5CC-452C-AA86-E5E58F21EA40}"/>
+    <cellStyle name="Normal 3 2 4 2" xfId="3" xr:uid="{71652849-4109-4C98-A937-5DD92ACA3696}"/>
+    <cellStyle name="Normal 5" xfId="6" xr:uid="{58A5829F-0798-4AC5-A887-3CBCA8BB0153}"/>
+    <cellStyle name="Normal 8 2" xfId="4" xr:uid="{1E08BF75-563B-4006-9FB0-94126509CFF1}"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1611,7 +1627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1623,18 +1639,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="101">
-        <v>45194</v>
+        <v>40</v>
+      </c>
+      <c r="C1" s="104">
+        <v>45258</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1644,356 +1660,381 @@
     </row>
     <row r="5" spans="1:3">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="99" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="100"/>
+      <c r="A13" s="102" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="103"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="97" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="98"/>
+      <c r="A23" s="100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="101"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{E8E2C6EE-F51D-430F-B52A-741CFFD15A20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25"/>
+  <sheetFormatPr defaultRowHeight="8.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
     <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
-    <col min="17" max="20" width="9.140625" style="4" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="4"/>
+    <col min="17" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="104" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
+    <row r="1" spans="1:16" ht="15">
+      <c r="A1" s="106" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="95"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-    </row>
-    <row r="3" spans="1:16" ht="9" customHeight="1">
-      <c r="A3" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="92" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="14.85" customHeight="1">
-      <c r="A4" s="91"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="106"/>
-      <c r="M4" s="106"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="106"/>
-      <c r="P4" s="107"/>
-    </row>
-    <row r="5" spans="1:16" ht="9" customHeight="1">
-      <c r="A5" s="76"/>
-      <c r="B5" s="108" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="110" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="109"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="112" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="109"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="110" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="109"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="109"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+    </row>
+    <row r="3" spans="1:16" ht="9">
+      <c r="A3" s="97" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="95" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="94"/>
+      <c r="B4" s="107" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="109"/>
+    </row>
+    <row r="5" spans="1:16" ht="9">
+      <c r="A5" s="79"/>
+      <c r="B5" s="110" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="112" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="111"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="111"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" s="111"/>
       <c r="P5" s="114"/>
     </row>
-    <row r="6" spans="1:16" ht="9" customHeight="1">
-      <c r="A6" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="89"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="84"/>
-    </row>
-    <row r="7" spans="1:16" ht="9" customHeight="1">
-      <c r="A7" s="76"/>
-      <c r="B7" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="82" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="82"/>
-      <c r="E7" s="83" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="82"/>
-      <c r="K7" s="81" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7" s="80"/>
-      <c r="N7" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="P7" s="78"/>
-    </row>
-    <row r="8" spans="1:16" ht="9" customHeight="1">
-      <c r="A8" s="76"/>
-      <c r="B8" s="76" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="82" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="83" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="76" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="80" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="79" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="76" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="82" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="81" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="76" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="80" t="s">
-        <v>34</v>
-      </c>
-      <c r="N8" s="79" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" s="76" t="s">
-        <v>33</v>
-      </c>
-      <c r="P8" s="78" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="9" customHeight="1">
-      <c r="A9" s="71"/>
-      <c r="B9" s="71" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="75">
+    <row r="6" spans="1:16" ht="9">
+      <c r="A6" s="79" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="88" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="85"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="83"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="85"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="89"/>
+      <c r="O6" s="88"/>
+      <c r="P6" s="87"/>
+    </row>
+    <row r="7" spans="1:16" ht="9">
+      <c r="A7" s="79"/>
+      <c r="B7" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="86" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="82" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="84" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="83"/>
+      <c r="N7" s="82" t="s">
+        <v>67</v>
+      </c>
+      <c r="O7" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="P7" s="81" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="9">
+      <c r="A8" s="79"/>
+      <c r="B8" s="79" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="85" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="85" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="79" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="83" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="79" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="85" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="84" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="83" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="O8" s="79" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" s="81" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="9">
+      <c r="A9" s="74"/>
+      <c r="B9" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="78">
         <v>-1</v>
       </c>
-      <c r="D9" s="75"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="76">
+      <c r="D9" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="80"/>
+      <c r="F9" s="79">
         <v>-1</v>
       </c>
-      <c r="G9" s="73"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="71">
+      <c r="G9" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="75"/>
+      <c r="I9" s="74">
         <v>-1</v>
       </c>
-      <c r="J9" s="75"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="71">
+      <c r="J9" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="74">
         <v>-1</v>
       </c>
-      <c r="M9" s="73"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="71">
+      <c r="M9" s="76"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="74">
         <v>-1</v>
       </c>
-      <c r="P9" s="70"/>
-    </row>
-    <row r="10" spans="1:16" ht="9" customHeight="1">
+      <c r="P9" s="73" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="9">
       <c r="A10" s="19" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12">
         <v>1993089</v>
@@ -2010,7 +2051,7 @@
       <c r="F10" s="30">
         <v>132</v>
       </c>
-      <c r="G10" s="69">
+      <c r="G10" s="72">
         <v>5624</v>
       </c>
       <c r="H10" s="13">
@@ -2041,14 +2082,14 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="9" customHeight="1">
+    <row r="11" spans="1:16" ht="9">
       <c r="A11" s="19" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B11" s="12">
         <v>167313</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="53">
         <v>3831</v>
       </c>
       <c r="D11" s="26">
@@ -2060,13 +2101,13 @@
       <c r="F11" s="17">
         <v>598</v>
       </c>
-      <c r="G11" s="68">
+      <c r="G11" s="71">
         <v>8620</v>
       </c>
       <c r="H11" s="28">
         <v>571380</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="53">
         <v>14901</v>
       </c>
       <c r="J11" s="26">
@@ -2091,14 +2132,14 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="9" customHeight="1">
+    <row r="12" spans="1:16" ht="9">
       <c r="A12" s="19" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B12" s="12">
         <v>2391632</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="53">
         <v>18386</v>
       </c>
       <c r="D12" s="26">
@@ -2110,13 +2151,13 @@
       <c r="F12" s="17">
         <v>7033</v>
       </c>
-      <c r="G12" s="68">
+      <c r="G12" s="71">
         <v>8486</v>
       </c>
       <c r="H12" s="28">
         <v>3479891</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="53">
         <v>34312</v>
       </c>
       <c r="J12" s="26">
@@ -2141,9 +2182,9 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="9" customHeight="1">
+    <row r="13" spans="1:16" ht="9">
       <c r="A13" s="19" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B13" s="12">
         <v>860646</v>
@@ -2151,7 +2192,7 @@
       <c r="C13" s="12">
         <v>11791</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="62">
         <v>872437</v>
       </c>
       <c r="E13" s="10">
@@ -2160,7 +2201,7 @@
       <c r="F13" s="41">
         <v>722</v>
       </c>
-      <c r="G13" s="67">
+      <c r="G13" s="70">
         <v>12044</v>
       </c>
       <c r="H13" s="13">
@@ -2169,7 +2210,7 @@
       <c r="I13" s="12">
         <v>27332</v>
       </c>
-      <c r="J13" s="63">
+      <c r="J13" s="64">
         <v>1859091</v>
       </c>
       <c r="K13" s="15">
@@ -2178,7 +2219,7 @@
       <c r="L13" s="42">
         <v>1</v>
       </c>
-      <c r="M13" s="61">
+      <c r="M13" s="62">
         <v>169797</v>
       </c>
       <c r="N13" s="33">
@@ -2191,9 +2232,9 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="9" customHeight="1">
+    <row r="14" spans="1:16" ht="9">
       <c r="A14" s="52" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B14" s="51">
         <v>13957692</v>
@@ -2241,9 +2282,9 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="9" customHeight="1">
+    <row r="15" spans="1:16" ht="9">
       <c r="A15" s="19" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B15" s="12">
         <v>1623494</v>
@@ -2291,9 +2332,9 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="9" customHeight="1">
+    <row r="16" spans="1:16" ht="9">
       <c r="A16" s="19" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B16" s="12">
         <v>1210262</v>
@@ -2341,9 +2382,9 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="9" customHeight="1">
+    <row r="17" spans="1:16" ht="9">
       <c r="A17" s="43" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B17" s="42">
         <v>414460</v>
@@ -2351,7 +2392,7 @@
       <c r="C17" s="42">
         <v>1455</v>
       </c>
-      <c r="D17" s="63">
+      <c r="D17" s="64">
         <v>415915</v>
       </c>
       <c r="E17" s="18">
@@ -2360,7 +2401,7 @@
       <c r="F17" s="41">
         <v>468</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="62">
         <v>3859</v>
       </c>
       <c r="H17" s="33">
@@ -2369,16 +2410,16 @@
       <c r="I17" s="42">
         <v>3247</v>
       </c>
-      <c r="J17" s="63">
+      <c r="J17" s="64">
         <v>582338</v>
       </c>
-      <c r="K17" s="62">
+      <c r="K17" s="63">
         <v>4023</v>
       </c>
       <c r="L17" s="42">
         <v>0</v>
       </c>
-      <c r="M17" s="61">
+      <c r="M17" s="62">
         <v>4023</v>
       </c>
       <c r="N17" s="33">
@@ -2391,9 +2432,9 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="9" customHeight="1">
+    <row r="18" spans="1:16" ht="9">
       <c r="A18" s="19" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B18" s="12">
         <v>191873</v>
@@ -2441,14 +2482,14 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="9" customHeight="1">
+    <row r="19" spans="1:16" ht="9">
       <c r="A19" s="19" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B19" s="12">
         <v>7736727</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="69">
         <v>104826</v>
       </c>
       <c r="D19" s="26">
@@ -2466,7 +2507,7 @@
       <c r="H19" s="28">
         <v>9792260</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="69">
         <v>150443</v>
       </c>
       <c r="J19" s="26">
@@ -2491,14 +2532,14 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="9" customHeight="1">
+    <row r="20" spans="1:16" ht="9">
       <c r="A20" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="12">
         <v>3444115</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="53">
         <v>51306</v>
       </c>
       <c r="D20" s="26">
@@ -2516,7 +2557,7 @@
       <c r="H20" s="28">
         <v>5006420</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="53">
         <v>83196</v>
       </c>
       <c r="J20" s="26">
@@ -2541,9 +2582,9 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="9" customHeight="1">
+    <row r="21" spans="1:16" ht="9">
       <c r="A21" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="12">
         <v>468176</v>
@@ -2591,9 +2632,9 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="9" customHeight="1">
+    <row r="22" spans="1:16" ht="9">
       <c r="A22" s="52" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B22" s="51">
         <v>586008</v>
@@ -2631,7 +2672,7 @@
       <c r="M22" s="23">
         <v>59225</v>
       </c>
-      <c r="N22" s="54">
+      <c r="N22" s="55">
         <v>1906586</v>
       </c>
       <c r="O22" s="21">
@@ -2641,9 +2682,9 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="9" customHeight="1">
+    <row r="23" spans="1:16" ht="9">
       <c r="A23" s="19" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B23" s="12">
         <v>4126473</v>
@@ -2691,9 +2732,9 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="9" customHeight="1">
+    <row r="24" spans="1:16" ht="9">
       <c r="A24" s="19" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B24" s="12">
         <v>2121269</v>
@@ -2741,9 +2782,9 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="9" customHeight="1">
+    <row r="25" spans="1:16" ht="9">
       <c r="A25" s="43" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B25" s="42">
         <v>1153267</v>
@@ -2781,7 +2822,7 @@
       <c r="M25" s="34">
         <v>191804</v>
       </c>
-      <c r="N25" s="53">
+      <c r="N25" s="54">
         <v>3747148</v>
       </c>
       <c r="O25" s="32">
@@ -2791,9 +2832,9 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="9" customHeight="1">
+    <row r="26" spans="1:16" ht="9">
       <c r="A26" s="19" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B26" s="12">
         <v>885177</v>
@@ -2841,14 +2882,14 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="9" customHeight="1">
+    <row r="27" spans="1:16" ht="9">
       <c r="A27" s="19" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B27" s="12">
         <v>1613475</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="53">
         <v>31022</v>
       </c>
       <c r="D27" s="26">
@@ -2866,7 +2907,7 @@
       <c r="H27" s="28">
         <v>2652943</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="53">
         <v>54101</v>
       </c>
       <c r="J27" s="26">
@@ -2891,9 +2932,9 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="9" customHeight="1">
+    <row r="28" spans="1:16" ht="9">
       <c r="A28" s="19" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B28" s="12">
         <v>1288404</v>
@@ -2941,9 +2982,9 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="9" customHeight="1">
+    <row r="29" spans="1:16" ht="9">
       <c r="A29" s="19" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B29" s="21">
         <v>352449</v>
@@ -2951,7 +2992,7 @@
       <c r="C29" s="12">
         <v>3630</v>
       </c>
-      <c r="D29" s="61">
+      <c r="D29" s="62">
         <v>356079</v>
       </c>
       <c r="E29" s="18">
@@ -2960,7 +3001,7 @@
       <c r="F29" s="41">
         <v>3137</v>
       </c>
-      <c r="G29" s="61">
+      <c r="G29" s="62">
         <v>4623</v>
       </c>
       <c r="H29" s="33">
@@ -2969,16 +3010,16 @@
       <c r="I29" s="42">
         <v>8406</v>
       </c>
-      <c r="J29" s="63">
+      <c r="J29" s="64">
         <v>722064</v>
       </c>
-      <c r="K29" s="62">
+      <c r="K29" s="63">
         <v>38319</v>
       </c>
       <c r="L29" s="42">
         <v>21</v>
       </c>
-      <c r="M29" s="61">
+      <c r="M29" s="62">
         <v>38340</v>
       </c>
       <c r="N29" s="33">
@@ -2991,9 +3032,9 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="9" customHeight="1">
+    <row r="30" spans="1:16" ht="9">
       <c r="A30" s="52" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B30" s="51">
         <v>1795964</v>
@@ -3041,17 +3082,17 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="9" customHeight="1">
+    <row r="31" spans="1:16" ht="9">
       <c r="A31" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="45">
+        <v>37</v>
+      </c>
+      <c r="B31" s="65">
         <v>1999889</v>
       </c>
-      <c r="C31" s="45">
+      <c r="C31" s="65">
         <v>3484</v>
       </c>
-      <c r="D31" s="66">
+      <c r="D31" s="68">
         <v>2003373</v>
       </c>
       <c r="E31" s="29">
@@ -3060,40 +3101,40 @@
       <c r="F31" s="17">
         <v>242</v>
       </c>
-      <c r="G31" s="64">
+      <c r="G31" s="66">
         <v>13752</v>
       </c>
       <c r="H31" s="44">
         <v>2870674</v>
       </c>
-      <c r="I31" s="45">
+      <c r="I31" s="65">
         <v>10764</v>
       </c>
-      <c r="J31" s="66">
+      <c r="J31" s="68">
         <v>2881438</v>
       </c>
-      <c r="K31" s="65">
+      <c r="K31" s="67">
         <v>137409</v>
       </c>
-      <c r="L31" s="45">
+      <c r="L31" s="65">
         <v>714</v>
       </c>
-      <c r="M31" s="64">
+      <c r="M31" s="66">
         <v>138123</v>
       </c>
       <c r="N31" s="44">
         <v>5021482</v>
       </c>
-      <c r="O31" s="45">
+      <c r="O31" s="65">
         <v>15204</v>
       </c>
-      <c r="P31" s="45">
+      <c r="P31" s="65">
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="9" customHeight="1">
+    <row r="32" spans="1:16" ht="9">
       <c r="A32" s="19" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B32" s="12">
         <v>2671737</v>
@@ -3141,9 +3182,9 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="9" customHeight="1">
+    <row r="33" spans="1:16" ht="9">
       <c r="A33" s="43" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B33" s="42">
         <v>1827137</v>
@@ -3151,7 +3192,7 @@
       <c r="C33" s="42">
         <v>14553</v>
       </c>
-      <c r="D33" s="63">
+      <c r="D33" s="64">
         <v>1841690</v>
       </c>
       <c r="E33" s="18">
@@ -3160,7 +3201,7 @@
       <c r="F33" s="41">
         <v>5763</v>
       </c>
-      <c r="G33" s="61">
+      <c r="G33" s="62">
         <v>19192</v>
       </c>
       <c r="H33" s="33">
@@ -3169,16 +3210,16 @@
       <c r="I33" s="42">
         <v>31783</v>
       </c>
-      <c r="J33" s="63">
+      <c r="J33" s="64">
         <v>3585895</v>
       </c>
-      <c r="K33" s="62">
+      <c r="K33" s="63">
         <v>243972</v>
       </c>
       <c r="L33" s="42">
         <v>0</v>
       </c>
-      <c r="M33" s="61">
+      <c r="M33" s="62">
         <v>243972</v>
       </c>
       <c r="N33" s="33">
@@ -3191,14 +3232,14 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="9" customHeight="1">
+    <row r="34" spans="1:16" ht="9">
       <c r="A34" s="19" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B34" s="12">
         <v>786202</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="53">
         <v>2223</v>
       </c>
       <c r="D34" s="26">
@@ -3216,7 +3257,7 @@
       <c r="H34" s="28">
         <v>1226266</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="53">
         <v>6325</v>
       </c>
       <c r="J34" s="26">
@@ -3241,9 +3282,9 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="9" customHeight="1">
+    <row r="35" spans="1:16" ht="9">
       <c r="A35" s="19" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B35" s="12">
         <v>1975005</v>
@@ -3291,14 +3332,14 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="9" customHeight="1">
+    <row r="36" spans="1:16" ht="9">
       <c r="A36" s="19" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="B36" s="12">
         <v>458637</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="53">
         <v>444</v>
       </c>
       <c r="D36" s="26">
@@ -3316,7 +3357,7 @@
       <c r="H36" s="28">
         <v>1129447</v>
       </c>
-      <c r="I36" s="27">
+      <c r="I36" s="53">
         <v>3655</v>
       </c>
       <c r="J36" s="26">
@@ -3341,9 +3382,9 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="9" customHeight="1">
+    <row r="37" spans="1:16" ht="9">
       <c r="A37" s="19" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B37" s="12">
         <v>610897</v>
@@ -3378,7 +3419,7 @@
       <c r="L37" s="35">
         <v>96</v>
       </c>
-      <c r="M37" s="60">
+      <c r="M37" s="61">
         <v>50373</v>
       </c>
       <c r="N37" s="33">
@@ -3391,9 +3432,9 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="9" customHeight="1">
+    <row r="38" spans="1:16" ht="9">
       <c r="A38" s="52" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B38" s="51">
         <v>1020129</v>
@@ -3401,7 +3442,7 @@
       <c r="C38" s="51">
         <v>7374</v>
       </c>
-      <c r="D38" s="58">
+      <c r="D38" s="59">
         <v>1027503</v>
       </c>
       <c r="E38" s="29">
@@ -3410,25 +3451,25 @@
       <c r="F38" s="30">
         <v>2688</v>
       </c>
-      <c r="G38" s="56">
+      <c r="G38" s="57">
         <v>3209</v>
       </c>
-      <c r="H38" s="59">
+      <c r="H38" s="60">
         <v>1435681</v>
       </c>
       <c r="I38" s="51">
         <v>13608</v>
       </c>
-      <c r="J38" s="58">
+      <c r="J38" s="59">
         <v>1449289</v>
       </c>
-      <c r="K38" s="57">
+      <c r="K38" s="58">
         <v>69356</v>
       </c>
       <c r="L38" s="51">
         <v>0</v>
       </c>
-      <c r="M38" s="56">
+      <c r="M38" s="57">
         <v>69356</v>
       </c>
       <c r="N38" s="22">
@@ -3441,9 +3482,9 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="9" customHeight="1">
+    <row r="39" spans="1:16" ht="9">
       <c r="A39" s="19" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B39" s="12">
         <v>458256</v>
@@ -3491,9 +3532,9 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="9" customHeight="1">
+    <row r="40" spans="1:16" ht="9">
       <c r="A40" s="19" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B40" s="12">
         <v>2518878</v>
@@ -3541,9 +3582,9 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="9" customHeight="1">
+    <row r="41" spans="1:16" ht="9">
       <c r="A41" s="43" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="B41" s="42">
         <v>617536</v>
@@ -3591,9 +3632,9 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="9" customHeight="1">
+    <row r="42" spans="1:16" ht="9">
       <c r="A42" s="19" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="B42" s="12">
         <v>4214023</v>
@@ -3616,7 +3657,7 @@
       <c r="H42" s="28">
         <v>6585225</v>
       </c>
-      <c r="I42" s="27">
+      <c r="I42" s="53">
         <v>40480</v>
       </c>
       <c r="J42" s="26">
@@ -3641,9 +3682,9 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="9" customHeight="1">
+    <row r="43" spans="1:16" ht="9">
       <c r="A43" s="19" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="B43" s="12">
         <v>3352960</v>
@@ -3666,7 +3707,7 @@
       <c r="H43" s="28">
         <v>5042146</v>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="53">
         <v>75652</v>
       </c>
       <c r="J43" s="26">
@@ -3691,9 +3732,9 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="9" customHeight="1">
+    <row r="44" spans="1:16" ht="9">
       <c r="A44" s="19" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="B44" s="12">
         <v>211955</v>
@@ -3716,7 +3757,7 @@
       <c r="H44" s="28">
         <v>630951</v>
       </c>
-      <c r="I44" s="27">
+      <c r="I44" s="53">
         <v>12581</v>
       </c>
       <c r="J44" s="26">
@@ -3741,11 +3782,11 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="9" customHeight="1">
+    <row r="45" spans="1:16" ht="9">
       <c r="A45" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45" s="55">
+        <v>23</v>
+      </c>
+      <c r="B45" s="56">
         <v>4208938</v>
       </c>
       <c r="C45" s="45">
@@ -3791,9 +3832,9 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="9" customHeight="1">
+    <row r="46" spans="1:16" ht="9">
       <c r="A46" s="52" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="B46" s="51">
         <v>1218261</v>
@@ -3831,7 +3872,7 @@
       <c r="M46" s="23">
         <v>133895</v>
       </c>
-      <c r="N46" s="54">
+      <c r="N46" s="55">
         <v>3708789</v>
       </c>
       <c r="O46" s="46">
@@ -3841,9 +3882,9 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="9" customHeight="1">
+    <row r="47" spans="1:16" ht="9">
       <c r="A47" s="19" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="B47" s="12">
         <v>1416471</v>
@@ -3891,9 +3932,9 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="9" customHeight="1">
+    <row r="48" spans="1:16" ht="9">
       <c r="A48" s="19" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="B48" s="12">
         <v>3999144</v>
@@ -3941,9 +3982,9 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="9" customHeight="1">
+    <row r="49" spans="1:16" ht="9">
       <c r="A49" s="43" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B49" s="42">
         <v>374939</v>
@@ -3981,7 +4022,7 @@
       <c r="M49" s="34">
         <v>23607</v>
       </c>
-      <c r="N49" s="53">
+      <c r="N49" s="54">
         <v>849912</v>
       </c>
       <c r="O49" s="21">
@@ -3991,9 +4032,9 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="9" customHeight="1">
+    <row r="50" spans="1:16" ht="9">
       <c r="A50" s="19" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="B50" s="12">
         <v>1692051</v>
@@ -4016,7 +4057,7 @@
       <c r="H50" s="28">
         <v>2545151</v>
       </c>
-      <c r="I50" s="27">
+      <c r="I50" s="53">
         <v>117820</v>
       </c>
       <c r="J50" s="26">
@@ -4041,9 +4082,9 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="9" customHeight="1">
+    <row r="51" spans="1:16" ht="9">
       <c r="A51" s="19" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="B51" s="12">
         <v>319820</v>
@@ -4091,9 +4132,9 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="9" customHeight="1">
+    <row r="52" spans="1:16" ht="9">
       <c r="A52" s="19" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="B52" s="12">
         <v>2069406</v>
@@ -4116,7 +4157,7 @@
       <c r="H52" s="28">
         <v>3451227</v>
       </c>
-      <c r="I52" s="27">
+      <c r="I52" s="53">
         <v>81684</v>
       </c>
       <c r="J52" s="26">
@@ -4141,9 +4182,9 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="9" customHeight="1">
+    <row r="53" spans="1:16" ht="9">
       <c r="A53" s="19" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="B53" s="12">
         <v>8000313</v>
@@ -4191,9 +4232,9 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="9" customHeight="1">
+    <row r="54" spans="1:16" ht="9">
       <c r="A54" s="52" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="B54" s="51">
         <v>891867</v>
@@ -4241,9 +4282,9 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="9" customHeight="1">
+    <row r="55" spans="1:16" ht="9">
       <c r="A55" s="19" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="B55" s="12">
         <v>189922</v>
@@ -4291,9 +4332,9 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="9" customHeight="1">
+    <row r="56" spans="1:16" ht="9">
       <c r="A56" s="19" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B56" s="12">
         <v>3014609</v>
@@ -4341,9 +4382,9 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="9" customHeight="1">
+    <row r="57" spans="1:16" ht="9">
       <c r="A57" s="43" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="B57" s="42">
         <v>2735895</v>
@@ -4391,9 +4432,9 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="9" customHeight="1">
+    <row r="58" spans="1:16" ht="9">
       <c r="A58" s="19" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B58" s="12">
         <v>497785</v>
@@ -4441,9 +4482,9 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="9" customHeight="1">
+    <row r="59" spans="1:16" ht="9">
       <c r="A59" s="19" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="B59" s="12">
         <v>1873334</v>
@@ -4491,9 +4532,9 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="9" customHeight="1">
+    <row r="60" spans="1:16" ht="9">
       <c r="A60" s="19" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="B60" s="12">
         <v>188354</v>
@@ -4541,9 +4582,9 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="9" customHeight="1">
+    <row r="61" spans="1:16" ht="9">
       <c r="A61" s="11" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B61" s="7">
         <v>103796315</v>
@@ -4591,7 +4632,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="9" customHeight="1">
+    <row r="62" spans="1:16" ht="9">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4610,24 +4651,24 @@
       <c r="P62" s="5"/>
     </row>
     <row r="63" spans="1:16" ht="39.6" customHeight="1">
-      <c r="A63" s="102" t="s">
-        <v>88</v>
-      </c>
-      <c r="B63" s="103"/>
-      <c r="C63" s="103"/>
-      <c r="D63" s="103"/>
-      <c r="E63" s="103"/>
-      <c r="F63" s="103"/>
-      <c r="G63" s="103"/>
-      <c r="H63" s="103"/>
-      <c r="I63" s="103"/>
-      <c r="J63" s="103"/>
-      <c r="K63" s="103"/>
-      <c r="L63" s="103"/>
-      <c r="M63" s="103"/>
-      <c r="N63" s="103"/>
-      <c r="O63" s="103"/>
-      <c r="P63" s="103"/>
+      <c r="A63" s="105" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="105"/>
+      <c r="C63" s="105"/>
+      <c r="D63" s="105"/>
+      <c r="E63" s="105"/>
+      <c r="F63" s="105"/>
+      <c r="G63" s="105"/>
+      <c r="H63" s="105"/>
+      <c r="I63" s="105"/>
+      <c r="J63" s="105"/>
+      <c r="K63" s="105"/>
+      <c r="L63" s="105"/>
+      <c r="M63" s="105"/>
+      <c r="N63" s="105"/>
+      <c r="O63" s="105"/>
+      <c r="P63" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4671,12 +4712,12 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B78ABCA-933B-4659-9B31-0CC7983DEE50}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -4688,31 +4729,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="96" t="s">
-        <v>89</v>
+      <c r="A1" s="99" t="s">
+        <v>85</v>
       </c>
       <c r="B1" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C1" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E1" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F1" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -4735,7 +4776,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4758,7 +4799,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4781,7 +4822,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4804,7 +4845,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4827,7 +4868,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4850,7 +4891,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4873,7 +4914,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4896,7 +4937,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4919,7 +4960,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4942,7 +4983,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4965,7 +5006,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4988,7 +5029,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5011,7 +5052,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -5034,7 +5075,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -5057,7 +5098,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -5080,7 +5121,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -5103,7 +5144,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -5126,7 +5167,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5149,7 +5190,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5172,7 +5213,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5195,7 +5236,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5218,7 +5259,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -5241,7 +5282,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -5264,7 +5305,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -5287,7 +5328,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -5310,7 +5351,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -5333,7 +5374,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -5356,7 +5397,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -5379,7 +5420,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -5402,7 +5443,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5425,7 +5466,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -5448,7 +5489,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -5471,7 +5512,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -5494,7 +5535,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -5517,7 +5558,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5540,7 +5581,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5563,7 +5604,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -5586,7 +5627,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5609,7 +5650,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5632,7 +5673,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5655,7 +5696,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5678,7 +5719,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -5701,7 +5742,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -5724,7 +5765,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -5747,7 +5788,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5770,7 +5811,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -5793,7 +5834,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -5816,7 +5857,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -5839,7 +5880,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -5862,7 +5903,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5885,7 +5926,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -5908,7 +5949,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -5931,7 +5972,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -5954,7 +5995,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -5977,7 +6018,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -6000,7 +6041,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -6023,7 +6064,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -6046,7 +6087,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -6069,7 +6110,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -6091,12 +6132,13 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB4474D-CAD8-4EF6-BCA5-F1268C4006F3}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -6108,31 +6150,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="96" t="s">
-        <v>89</v>
+      <c r="A1" s="99" t="s">
+        <v>85</v>
       </c>
       <c r="B1" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C1" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E1" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F1" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -6155,7 +6197,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6178,7 +6220,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6201,7 +6243,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6224,7 +6266,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6247,7 +6289,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6270,7 +6312,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6293,7 +6335,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6316,7 +6358,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -6339,7 +6381,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6362,7 +6404,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6385,7 +6427,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6408,7 +6450,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6431,7 +6473,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6454,7 +6496,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6477,7 +6519,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6500,7 +6542,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6523,7 +6565,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -6546,7 +6588,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6569,7 +6611,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6592,7 +6634,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6615,7 +6657,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6638,7 +6680,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6661,7 +6703,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6684,7 +6726,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -6707,7 +6749,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6730,7 +6772,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -6753,7 +6795,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -6776,7 +6818,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -6799,7 +6841,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -6822,7 +6864,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -6845,7 +6887,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -6868,7 +6910,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -6891,7 +6933,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -6914,7 +6956,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -6937,7 +6979,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -6960,7 +7002,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -6983,7 +7025,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -7006,7 +7048,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -7029,7 +7071,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -7052,7 +7094,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -7075,7 +7117,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -7098,7 +7140,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -7121,7 +7163,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -7144,7 +7186,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -7167,7 +7209,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -7190,7 +7232,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -7213,7 +7255,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -7236,7 +7278,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -7259,7 +7301,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -7282,7 +7324,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -7305,7 +7347,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -7328,7 +7370,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7351,7 +7393,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -7374,7 +7416,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -7397,7 +7439,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -7420,7 +7462,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -7443,7 +7485,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -7466,7 +7508,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -7489,7 +7531,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B61">
         <v>0</v>

--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\trans\VSbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CD04216-85BC-4523-9C8B-BD5B0166732F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0391AF53-B75B-4688-AD3B-EC6F8F300043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="13035" windowHeight="16890" firstSheet="2" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="1170" yWindow="705" windowWidth="25680" windowHeight="16185" firstSheet="2" activeTab="2" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1642,7 +1642,7 @@
         <v>40</v>
       </c>
       <c r="C1" s="104">
-        <v>45258</v>
+        <v>45267</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6192,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">

--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\trans\VSbS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/LA/trans/VSbS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0391AF53-B75B-4688-AD3B-EC6F8F300043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C69171C-244A-5542-A36B-94665995ECC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="705" windowWidth="25680" windowHeight="16185" firstSheet="2" activeTab="2" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="13840" windowHeight="12640" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1629,9 +1628,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="70.140625" customWidth="1"/>
+    <col min="2" max="2" width="70.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1642,7 +1641,7 @@
         <v>40</v>
       </c>
       <c r="C1" s="104">
-        <v>45267</v>
+        <v>45295</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1755,14 +1754,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr defaultRowHeight="8.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="10"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
-    <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
+    <col min="2" max="16" width="9.83203125" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15">
+    <row r="1" spans="1:16" ht="14">
       <c r="A1" s="106" t="s">
         <v>76</v>
       </c>
@@ -1800,7 +1799,7 @@
       <c r="O2" s="96"/>
       <c r="P2" s="96"/>
     </row>
-    <row r="3" spans="1:16" ht="9">
+    <row r="3" spans="1:16" ht="11">
       <c r="A3" s="97" t="s">
         <v>75</v>
       </c>
@@ -1842,7 +1841,7 @@
       <c r="O4" s="108"/>
       <c r="P4" s="109"/>
     </row>
-    <row r="5" spans="1:16" ht="9">
+    <row r="5" spans="1:16" ht="11">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>73</v>
@@ -1870,7 +1869,7 @@
       <c r="O5" s="111"/>
       <c r="P5" s="114"/>
     </row>
-    <row r="6" spans="1:16" ht="9">
+    <row r="6" spans="1:16" ht="11">
       <c r="A6" s="79" t="s">
         <v>68</v>
       </c>
@@ -1898,7 +1897,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="87"/>
     </row>
-    <row r="7" spans="1:16" ht="9">
+    <row r="7" spans="1:16" ht="11">
       <c r="A7" s="79"/>
       <c r="B7" s="79" t="s">
         <v>63</v>
@@ -1944,7 +1943,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="9">
+    <row r="8" spans="1:16" ht="11">
       <c r="A8" s="79"/>
       <c r="B8" s="79" t="s">
         <v>65</v>
@@ -1992,7 +1991,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="9">
+    <row r="9" spans="1:16" ht="11">
       <c r="A9" s="74"/>
       <c r="B9" s="74" t="s">
         <v>60</v>
@@ -2032,7 +2031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="9">
+    <row r="10" spans="1:16" ht="11">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -2082,7 +2081,7 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="9">
+    <row r="11" spans="1:16" ht="11">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="9">
+    <row r="12" spans="1:16" ht="11">
       <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="9">
+    <row r="13" spans="1:16" ht="11">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -2232,7 +2231,7 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="9">
+    <row r="14" spans="1:16" ht="11">
       <c r="A14" s="52" t="s">
         <v>54</v>
       </c>
@@ -2282,7 +2281,7 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="9">
+    <row r="15" spans="1:16" ht="11">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
@@ -2332,7 +2331,7 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="9">
+    <row r="16" spans="1:16" ht="11">
       <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
@@ -2382,7 +2381,7 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="9">
+    <row r="17" spans="1:16" ht="11">
       <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
@@ -2432,7 +2431,7 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="9">
+    <row r="18" spans="1:16" ht="11">
       <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
@@ -2482,7 +2481,7 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="9">
+    <row r="19" spans="1:16" ht="11">
       <c r="A19" s="19" t="s">
         <v>49</v>
       </c>
@@ -2532,7 +2531,7 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="9">
+    <row r="20" spans="1:16" ht="11">
       <c r="A20" s="19" t="s">
         <v>48</v>
       </c>
@@ -2582,7 +2581,7 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="9">
+    <row r="21" spans="1:16" ht="11">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -2632,7 +2631,7 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="9">
+    <row r="22" spans="1:16" ht="11">
       <c r="A22" s="52" t="s">
         <v>46</v>
       </c>
@@ -2682,7 +2681,7 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="9">
+    <row r="23" spans="1:16" ht="11">
       <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="9">
+    <row r="24" spans="1:16" ht="11">
       <c r="A24" s="19" t="s">
         <v>44</v>
       </c>
@@ -2782,7 +2781,7 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="9">
+    <row r="25" spans="1:16" ht="11">
       <c r="A25" s="43" t="s">
         <v>43</v>
       </c>
@@ -2832,7 +2831,7 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="9">
+    <row r="26" spans="1:16" ht="11">
       <c r="A26" s="19" t="s">
         <v>42</v>
       </c>
@@ -2882,7 +2881,7 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="9">
+    <row r="27" spans="1:16" ht="11">
       <c r="A27" s="19" t="s">
         <v>41</v>
       </c>
@@ -2932,7 +2931,7 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="9">
+    <row r="28" spans="1:16" ht="11">
       <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
@@ -2982,7 +2981,7 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="9">
+    <row r="29" spans="1:16" ht="11">
       <c r="A29" s="19" t="s">
         <v>39</v>
       </c>
@@ -3032,7 +3031,7 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="9">
+    <row r="30" spans="1:16" ht="11">
       <c r="A30" s="52" t="s">
         <v>38</v>
       </c>
@@ -3082,7 +3081,7 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="9">
+    <row r="31" spans="1:16" ht="11">
       <c r="A31" s="19" t="s">
         <v>37</v>
       </c>
@@ -3132,7 +3131,7 @@
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="9">
+    <row r="32" spans="1:16" ht="11">
       <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="9">
+    <row r="33" spans="1:16" ht="11">
       <c r="A33" s="43" t="s">
         <v>35</v>
       </c>
@@ -3232,7 +3231,7 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="9">
+    <row r="34" spans="1:16" ht="11">
       <c r="A34" s="19" t="s">
         <v>34</v>
       </c>
@@ -3282,7 +3281,7 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="9">
+    <row r="35" spans="1:16" ht="11">
       <c r="A35" s="19" t="s">
         <v>33</v>
       </c>
@@ -3332,7 +3331,7 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="9">
+    <row r="36" spans="1:16" ht="11">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -3382,7 +3381,7 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="9">
+    <row r="37" spans="1:16" ht="11">
       <c r="A37" s="19" t="s">
         <v>31</v>
       </c>
@@ -3432,7 +3431,7 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="9">
+    <row r="38" spans="1:16" ht="11">
       <c r="A38" s="52" t="s">
         <v>30</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="9">
+    <row r="39" spans="1:16" ht="11">
       <c r="A39" s="19" t="s">
         <v>29</v>
       </c>
@@ -3532,7 +3531,7 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="9">
+    <row r="40" spans="1:16" ht="11">
       <c r="A40" s="19" t="s">
         <v>28</v>
       </c>
@@ -3582,7 +3581,7 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="9">
+    <row r="41" spans="1:16" ht="11">
       <c r="A41" s="43" t="s">
         <v>27</v>
       </c>
@@ -3632,7 +3631,7 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="9">
+    <row r="42" spans="1:16" ht="11">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3682,7 +3681,7 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="9">
+    <row r="43" spans="1:16" ht="11">
       <c r="A43" s="19" t="s">
         <v>25</v>
       </c>
@@ -3732,7 +3731,7 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="9">
+    <row r="44" spans="1:16" ht="11">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -3782,7 +3781,7 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="9">
+    <row r="45" spans="1:16" ht="11">
       <c r="A45" s="19" t="s">
         <v>23</v>
       </c>
@@ -3832,7 +3831,7 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="9">
+    <row r="46" spans="1:16" ht="11">
       <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
@@ -3882,7 +3881,7 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="9">
+    <row r="47" spans="1:16" ht="11">
       <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
@@ -3932,7 +3931,7 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="9">
+    <row r="48" spans="1:16" ht="11">
       <c r="A48" s="19" t="s">
         <v>20</v>
       </c>
@@ -3982,7 +3981,7 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="9">
+    <row r="49" spans="1:16" ht="11">
       <c r="A49" s="43" t="s">
         <v>19</v>
       </c>
@@ -4032,7 +4031,7 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="9">
+    <row r="50" spans="1:16" ht="11">
       <c r="A50" s="19" t="s">
         <v>18</v>
       </c>
@@ -4082,7 +4081,7 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="9">
+    <row r="51" spans="1:16" ht="11">
       <c r="A51" s="19" t="s">
         <v>17</v>
       </c>
@@ -4132,7 +4131,7 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="9">
+    <row r="52" spans="1:16" ht="11">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -4182,7 +4181,7 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="9">
+    <row r="53" spans="1:16" ht="11">
       <c r="A53" s="19" t="s">
         <v>15</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="9">
+    <row r="54" spans="1:16" ht="11">
       <c r="A54" s="52" t="s">
         <v>14</v>
       </c>
@@ -4282,7 +4281,7 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="9">
+    <row r="55" spans="1:16" ht="11">
       <c r="A55" s="19" t="s">
         <v>13</v>
       </c>
@@ -4332,7 +4331,7 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="9">
+    <row r="56" spans="1:16" ht="11">
       <c r="A56" s="19" t="s">
         <v>12</v>
       </c>
@@ -4382,7 +4381,7 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="9">
+    <row r="57" spans="1:16" ht="11">
       <c r="A57" s="43" t="s">
         <v>11</v>
       </c>
@@ -4432,7 +4431,7 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="9">
+    <row r="58" spans="1:16" ht="11">
       <c r="A58" s="19" t="s">
         <v>10</v>
       </c>
@@ -4482,7 +4481,7 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="9">
+    <row r="59" spans="1:16" ht="11">
       <c r="A59" s="19" t="s">
         <v>9</v>
       </c>
@@ -4532,7 +4531,7 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="9">
+    <row r="60" spans="1:16" ht="11">
       <c r="A60" s="19" t="s">
         <v>8</v>
       </c>
@@ -4582,7 +4581,7 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="9">
+    <row r="61" spans="1:16" ht="11">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -4632,7 +4631,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="9">
+    <row r="62" spans="1:16" ht="11">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4650,7 +4649,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" ht="39.6" customHeight="1">
+    <row r="63" spans="1:16" ht="39.5" customHeight="1">
       <c r="A63" s="105" t="s">
         <v>6</v>
       </c>
@@ -4722,10 +4721,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6143,10 +6142,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6192,7 +6191,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">

--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/LA/trans/VSbS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\LA\trans\VSbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C69171C-244A-5542-A36B-94665995ECC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EE125CE-44B4-4EF3-9926-0EBB32C54E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="13840" windowHeight="12640" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12510" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1331,9 +1331,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1371,7 +1371,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1477,7 +1477,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1619,7 +1619,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1628,9 +1628,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="70.1640625" customWidth="1"/>
+    <col min="2" max="2" width="70.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1641,7 +1641,7 @@
         <v>40</v>
       </c>
       <c r="C1" s="104">
-        <v>45295</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1754,14 +1754,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="10"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
-    <col min="2" max="16" width="9.83203125" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.1640625" style="4"/>
+    <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
+    <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14">
+    <row r="1" spans="1:16" ht="15">
       <c r="A1" s="106" t="s">
         <v>76</v>
       </c>
@@ -1799,7 +1799,7 @@
       <c r="O2" s="96"/>
       <c r="P2" s="96"/>
     </row>
-    <row r="3" spans="1:16" ht="11">
+    <row r="3" spans="1:16" ht="9">
       <c r="A3" s="97" t="s">
         <v>75</v>
       </c>
@@ -1841,7 +1841,7 @@
       <c r="O4" s="108"/>
       <c r="P4" s="109"/>
     </row>
-    <row r="5" spans="1:16" ht="11">
+    <row r="5" spans="1:16" ht="9">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>73</v>
@@ -1869,7 +1869,7 @@
       <c r="O5" s="111"/>
       <c r="P5" s="114"/>
     </row>
-    <row r="6" spans="1:16" ht="11">
+    <row r="6" spans="1:16" ht="9">
       <c r="A6" s="79" t="s">
         <v>68</v>
       </c>
@@ -1897,7 +1897,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="87"/>
     </row>
-    <row r="7" spans="1:16" ht="11">
+    <row r="7" spans="1:16" ht="9">
       <c r="A7" s="79"/>
       <c r="B7" s="79" t="s">
         <v>63</v>
@@ -1943,7 +1943,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="11">
+    <row r="8" spans="1:16" ht="9">
       <c r="A8" s="79"/>
       <c r="B8" s="79" t="s">
         <v>65</v>
@@ -1991,7 +1991,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="11">
+    <row r="9" spans="1:16" ht="9">
       <c r="A9" s="74"/>
       <c r="B9" s="74" t="s">
         <v>60</v>
@@ -2031,7 +2031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="11">
+    <row r="10" spans="1:16" ht="9">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="11">
+    <row r="11" spans="1:16" ht="9">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="11">
+    <row r="12" spans="1:16" ht="9">
       <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="11">
+    <row r="13" spans="1:16" ht="9">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="11">
+    <row r="14" spans="1:16" ht="9">
       <c r="A14" s="52" t="s">
         <v>54</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="11">
+    <row r="15" spans="1:16" ht="9">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="11">
+    <row r="16" spans="1:16" ht="9">
       <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="11">
+    <row r="17" spans="1:16" ht="9">
       <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="11">
+    <row r="18" spans="1:16" ht="9">
       <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="11">
+    <row r="19" spans="1:16" ht="9">
       <c r="A19" s="19" t="s">
         <v>49</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="11">
+    <row r="20" spans="1:16" ht="9">
       <c r="A20" s="19" t="s">
         <v>48</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="11">
+    <row r="21" spans="1:16" ht="9">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="11">
+    <row r="22" spans="1:16" ht="9">
       <c r="A22" s="52" t="s">
         <v>46</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="11">
+    <row r="23" spans="1:16" ht="9">
       <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="11">
+    <row r="24" spans="1:16" ht="9">
       <c r="A24" s="19" t="s">
         <v>44</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="11">
+    <row r="25" spans="1:16" ht="9">
       <c r="A25" s="43" t="s">
         <v>43</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="11">
+    <row r="26" spans="1:16" ht="9">
       <c r="A26" s="19" t="s">
         <v>42</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="11">
+    <row r="27" spans="1:16" ht="9">
       <c r="A27" s="19" t="s">
         <v>41</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="11">
+    <row r="28" spans="1:16" ht="9">
       <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="11">
+    <row r="29" spans="1:16" ht="9">
       <c r="A29" s="19" t="s">
         <v>39</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="11">
+    <row r="30" spans="1:16" ht="9">
       <c r="A30" s="52" t="s">
         <v>38</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="11">
+    <row r="31" spans="1:16" ht="9">
       <c r="A31" s="19" t="s">
         <v>37</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="11">
+    <row r="32" spans="1:16" ht="9">
       <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="11">
+    <row r="33" spans="1:16" ht="9">
       <c r="A33" s="43" t="s">
         <v>35</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="11">
+    <row r="34" spans="1:16" ht="9">
       <c r="A34" s="19" t="s">
         <v>34</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="11">
+    <row r="35" spans="1:16" ht="9">
       <c r="A35" s="19" t="s">
         <v>33</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="11">
+    <row r="36" spans="1:16" ht="9">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="11">
+    <row r="37" spans="1:16" ht="9">
       <c r="A37" s="19" t="s">
         <v>31</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="11">
+    <row r="38" spans="1:16" ht="9">
       <c r="A38" s="52" t="s">
         <v>30</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="11">
+    <row r="39" spans="1:16" ht="9">
       <c r="A39" s="19" t="s">
         <v>29</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="11">
+    <row r="40" spans="1:16" ht="9">
       <c r="A40" s="19" t="s">
         <v>28</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="11">
+    <row r="41" spans="1:16" ht="9">
       <c r="A41" s="43" t="s">
         <v>27</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="11">
+    <row r="42" spans="1:16" ht="9">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="11">
+    <row r="43" spans="1:16" ht="9">
       <c r="A43" s="19" t="s">
         <v>25</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="11">
+    <row r="44" spans="1:16" ht="9">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="11">
+    <row r="45" spans="1:16" ht="9">
       <c r="A45" s="19" t="s">
         <v>23</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="11">
+    <row r="46" spans="1:16" ht="9">
       <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="11">
+    <row r="47" spans="1:16" ht="9">
       <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="11">
+    <row r="48" spans="1:16" ht="9">
       <c r="A48" s="19" t="s">
         <v>20</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="11">
+    <row r="49" spans="1:16" ht="9">
       <c r="A49" s="43" t="s">
         <v>19</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="11">
+    <row r="50" spans="1:16" ht="9">
       <c r="A50" s="19" t="s">
         <v>18</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="11">
+    <row r="51" spans="1:16" ht="9">
       <c r="A51" s="19" t="s">
         <v>17</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="11">
+    <row r="52" spans="1:16" ht="9">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="11">
+    <row r="53" spans="1:16" ht="9">
       <c r="A53" s="19" t="s">
         <v>15</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="11">
+    <row r="54" spans="1:16" ht="9">
       <c r="A54" s="52" t="s">
         <v>14</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="11">
+    <row r="55" spans="1:16" ht="9">
       <c r="A55" s="19" t="s">
         <v>13</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="11">
+    <row r="56" spans="1:16" ht="9">
       <c r="A56" s="19" t="s">
         <v>12</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="11">
+    <row r="57" spans="1:16" ht="9">
       <c r="A57" s="43" t="s">
         <v>11</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="11">
+    <row r="58" spans="1:16" ht="9">
       <c r="A58" s="19" t="s">
         <v>10</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="11">
+    <row r="59" spans="1:16" ht="9">
       <c r="A59" s="19" t="s">
         <v>9</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="11">
+    <row r="60" spans="1:16" ht="9">
       <c r="A60" s="19" t="s">
         <v>8</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="11">
+    <row r="61" spans="1:16" ht="9">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="11">
+    <row r="62" spans="1:16" ht="9">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4649,7 +4649,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" ht="39.5" customHeight="1">
+    <row r="63" spans="1:16" ht="39.6" customHeight="1">
       <c r="A63" s="105" t="s">
         <v>6</v>
       </c>
@@ -4721,10 +4721,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.6640625" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6142,10 +6142,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.6640625" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
